--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/KENTUCKY_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/KENTUCKY_2015.xlsx
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C234">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C592">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C617">
